--- a/datasets/xHI_EoR.xlsx
+++ b/datasets/xHI_EoR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas Soltinsky\Documents\astrophysics\website\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193461EB-FF04-4651-8642-452C73367F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D82C15-46D2-4D7C-BD10-C0F3EB8DD91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42900" yWindow="495" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="76">
   <si>
     <t>z</t>
   </si>
@@ -249,6 +252,21 @@
   </si>
   <si>
     <t>Umeda+25b</t>
+  </si>
+  <si>
+    <t>0,23-0,25</t>
+  </si>
+  <si>
+    <t>0,12-0,14</t>
+  </si>
+  <si>
+    <t>0,01-0,02</t>
+  </si>
+  <si>
+    <t>Lya effective optical depth, UV luminosity function, CMB optical depth</t>
+  </si>
+  <si>
+    <t>Qin+25</t>
   </si>
 </sst>
 </file>
@@ -309,7 +327,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -587,18 +605,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>6.1</v>
       </c>
@@ -658,7 +676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>5.9</v>
       </c>
@@ -684,7 +702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5.6</v>
       </c>
@@ -710,7 +728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>7.08</v>
       </c>
@@ -736,7 +754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>7.54</v>
       </c>
@@ -762,7 +780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7.54</v>
       </c>
@@ -788,7 +806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7.09</v>
       </c>
@@ -814,7 +832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -840,7 +858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7.5</v>
       </c>
@@ -866,7 +884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>7.9</v>
       </c>
@@ -898,7 +916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>7</v>
       </c>
@@ -924,7 +942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>7.5</v>
       </c>
@@ -956,7 +974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>7.6</v>
       </c>
@@ -988,7 +1006,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>6.7</v>
       </c>
@@ -1014,7 +1032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>7.3</v>
       </c>
@@ -1040,7 +1058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>7.3</v>
       </c>
@@ -1066,7 +1084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>7</v>
       </c>
@@ -1092,7 +1110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>6.6</v>
       </c>
@@ -1118,7 +1136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>5.95</v>
       </c>
@@ -1152,7 +1170,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>5.75</v>
       </c>
@@ -1186,7 +1204,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>5.55</v>
       </c>
@@ -1220,7 +1238,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>7.29</v>
       </c>
@@ -1246,7 +1264,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>6.9</v>
       </c>
@@ -1272,7 +1290,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>6.7</v>
       </c>
@@ -1298,7 +1316,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>6.5</v>
       </c>
@@ -1324,7 +1342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>6.3</v>
       </c>
@@ -1350,7 +1368,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>10.6</v>
       </c>
@@ -1376,7 +1394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>6</v>
       </c>
@@ -1408,7 +1426,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>5.9</v>
       </c>
@@ -1440,7 +1458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>5.8</v>
       </c>
@@ -1472,7 +1490,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>5.7</v>
       </c>
@@ -1504,7 +1522,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>5.6</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>5.5</v>
       </c>
@@ -1568,7 +1586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>5.4</v>
       </c>
@@ -1600,7 +1618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>5.3</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>5.2</v>
       </c>
@@ -1664,7 +1682,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>5.0999999999999996</v>
       </c>
@@ -1696,7 +1714,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>5</v>
       </c>
@@ -1728,7 +1746,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -1754,7 +1772,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>8</v>
       </c>
@@ -1780,7 +1798,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>7</v>
       </c>
@@ -1800,7 +1818,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>6.55</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>6.35</v>
       </c>
@@ -1864,7 +1882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>6.15</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>6.05</v>
       </c>
@@ -1928,7 +1946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>5.95</v>
       </c>
@@ -1960,7 +1978,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>5.9</v>
       </c>
@@ -1992,7 +2010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>6.87</v>
       </c>
@@ -2024,7 +2042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>6.46</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>6.1</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>9.8010000000000002</v>
       </c>
@@ -2120,7 +2138,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>7.96</v>
       </c>
@@ -2152,7 +2170,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>7.452</v>
       </c>
@@ -2184,7 +2202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>7.14</v>
       </c>
@@ -2216,7 +2234,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2242,7 +2260,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>57</v>
       </c>
@@ -2268,7 +2286,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -2294,7 +2312,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>6.3</v>
       </c>
@@ -2320,7 +2338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>7</v>
       </c>
@@ -2346,7 +2364,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>11</v>
       </c>
@@ -2378,7 +2396,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>8.41</v>
       </c>
@@ -2410,7 +2428,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>6.96</v>
       </c>
@@ -2442,7 +2460,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>5.9</v>
       </c>
@@ -2474,7 +2492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>9.3000000000000007</v>
       </c>
@@ -2506,7 +2524,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>6.5</v>
       </c>
@@ -2538,7 +2556,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>7.3</v>
       </c>
@@ -2564,7 +2582,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>7</v>
       </c>
@@ -2590,7 +2608,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>6.6</v>
       </c>
@@ -2616,7 +2634,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>6.6</v>
       </c>
@@ -2642,7 +2660,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>5.7</v>
       </c>
@@ -2668,7 +2686,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>5.7</v>
       </c>
@@ -2694,7 +2712,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>10.4</v>
       </c>
@@ -2720,7 +2738,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>8.6</v>
       </c>
@@ -2746,7 +2764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>7</v>
       </c>
@@ -2772,7 +2790,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>5.8</v>
       </c>
@@ -2798,7 +2816,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>5</v>
       </c>
@@ -2822,6 +2840,48 @@
       </c>
       <c r="J77" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>6.48</v>
+      </c>
+      <c r="D78" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78" t="s">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>6.05</v>
+      </c>
+      <c r="D79" t="s">
+        <v>72</v>
+      </c>
+      <c r="I79" t="s">
+        <v>74</v>
+      </c>
+      <c r="J79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>5.51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>73</v>
+      </c>
+      <c r="I80" t="s">
+        <v>74</v>
+      </c>
+      <c r="J80" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2830,6 +2890,6 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>